--- a/pitt-addresses.xlsx
+++ b/pitt-addresses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/ajkrall_pitt_edu/Documents/★ DSS/★ DSS General Info/Pitt Info/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAM688\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="735" documentId="11_957E3F5D93D17633E45E660EBAC442B793488C7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9038E33B-123E-43C1-A7BF-0BF9E33FB5B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604E7FD-B56E-49A7-9AAD-48D2913D63BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Values_3308834" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Places we have delivered'!$A$1:$G$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Values_3308834!$A$1:$G$386</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Values_3308834!$A$1:$G$387</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="1134">
   <si>
     <t>State</t>
   </si>
@@ -3434,6 +3434,15 @@
   </si>
   <si>
     <t>TOWRA</t>
+  </si>
+  <si>
+    <t>SALKP</t>
+  </si>
+  <si>
+    <t>Salk Pavilion</t>
+  </si>
+  <si>
+    <t>335 Sutherland Drive</t>
   </si>
 </sst>
 </file>
@@ -3975,12 +3984,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3990,12 +3999,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4043,7 +4052,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -4057,62 +4066,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4421,7 +4374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G386"/>
+  <dimension ref="A1:G387"/>
   <sheetFormatPr defaultColWidth="82.28515625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
@@ -10807,19 +10760,19 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="11" t="s">
-        <v>762</v>
+        <v>1131</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>763</v>
+        <v>1132</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>761</v>
+        <v>1133</v>
       </c>
       <c r="D278" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E278" s="12">
-        <v>15261</v>
+        <v>15213</v>
       </c>
       <c r="F278" s="12" t="s">
         <v>6</v>
@@ -10830,65 +10783,65 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="11" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C279" s="11" t="s">
-        <v>100</v>
+        <v>761</v>
       </c>
       <c r="D279" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E279" s="12">
-        <v>16701</v>
+        <v>15261</v>
       </c>
       <c r="F279" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1097</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="11" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>768</v>
+        <v>100</v>
       </c>
       <c r="D280" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E280" s="12">
-        <v>15261</v>
+        <v>16701</v>
       </c>
       <c r="F280" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1073</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="11" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B281" s="11" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C281" s="11" t="s">
-        <v>38</v>
+        <v>768</v>
       </c>
       <c r="D281" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E281" s="12">
-        <v>15213</v>
+        <v>15261</v>
       </c>
       <c r="F281" s="12" t="s">
         <v>6</v>
@@ -10899,157 +10852,157 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="11" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>773</v>
+        <v>38</v>
       </c>
       <c r="D282" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E282" s="12">
-        <v>17055</v>
+        <v>15213</v>
       </c>
       <c r="F282" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1094</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="11" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C283" s="11" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D283" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E283" s="12">
-        <v>16701</v>
+        <v>17055</v>
       </c>
       <c r="F283" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="11" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B284" s="11" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D284" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E284" s="12">
-        <v>15260</v>
+        <v>16701</v>
       </c>
       <c r="F284" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1073</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="11" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="C285" s="11" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="D285" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E285" s="12">
-        <v>15232</v>
+        <v>15260</v>
       </c>
       <c r="F285" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="11" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B286" s="11" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D286" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E286" s="12">
-        <v>15601</v>
+        <v>15232</v>
       </c>
       <c r="F286" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1092</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="11" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B287" s="11" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C287" s="11" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D287" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E287" s="12">
-        <v>15213</v>
+        <v>15601</v>
       </c>
       <c r="F287" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="11" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B288" s="11" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D288" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E288" s="12">
-        <v>15260</v>
+        <v>15213</v>
       </c>
       <c r="F288" s="12" t="s">
         <v>6</v>
@@ -11060,13 +11013,13 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" s="11" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C289" s="11" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D289" s="12" t="s">
         <v>5</v>
@@ -11083,19 +11036,19 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="11" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D290" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E290" s="12">
-        <v>15213</v>
+        <v>15260</v>
       </c>
       <c r="F290" s="12" t="s">
         <v>6</v>
@@ -11106,134 +11059,134 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" s="11" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C291" s="11" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D291" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E291" s="12">
-        <v>16701</v>
+        <v>15213</v>
       </c>
       <c r="F291" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1097</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" s="11" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D292" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E292" s="12">
-        <v>15904</v>
+        <v>16701</v>
       </c>
       <c r="F292" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" s="11" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C293" s="11" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D293" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E293" s="12">
-        <v>15217</v>
+        <v>15904</v>
       </c>
       <c r="F293" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1074</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" s="11" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>1063</v>
+        <v>807</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D294" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E294" s="12">
-        <v>15201</v>
+        <v>15217</v>
       </c>
       <c r="F294" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1099</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" s="11" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B295" s="11" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D295" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E295" s="12">
-        <v>15213</v>
+        <v>15201</v>
       </c>
       <c r="F295" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1073</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" s="11" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B296" s="11" t="s">
-        <v>814</v>
+        <v>1064</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D296" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E296" s="12">
-        <v>15260</v>
+        <v>15213</v>
       </c>
       <c r="F296" s="12" t="s">
         <v>6</v>
@@ -11244,19 +11197,19 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" s="11" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D297" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E297" s="12">
-        <v>15213</v>
+        <v>15260</v>
       </c>
       <c r="F297" s="12" t="s">
         <v>6</v>
@@ -11267,56 +11220,56 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" s="11" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E298" s="12">
-        <v>15904</v>
+        <v>15213</v>
       </c>
       <c r="F298" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" s="11" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>103</v>
+        <v>820</v>
       </c>
       <c r="D299" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E299" s="12">
-        <v>16354</v>
+        <v>15904</v>
       </c>
       <c r="F299" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" s="11" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C300" s="11" t="s">
         <v>103</v>
@@ -11336,36 +11289,36 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" s="11" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C301" s="11" t="s">
-        <v>827</v>
+        <v>103</v>
       </c>
       <c r="D301" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E301" s="12">
-        <v>15904</v>
+        <v>16354</v>
       </c>
       <c r="F301" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" s="11" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D302" s="12" t="s">
         <v>5</v>
@@ -11382,59 +11335,59 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" s="11" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="D303" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E303" s="12">
-        <v>15213</v>
+        <v>15904</v>
       </c>
       <c r="F303" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1073</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" s="11" t="s">
-        <v>830</v>
+        <v>780</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>831</v>
+        <v>781</v>
       </c>
       <c r="C304" s="11" t="s">
-        <v>831</v>
+        <v>782</v>
       </c>
       <c r="D304" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E304" s="12">
-        <v>16701</v>
+        <v>15213</v>
       </c>
       <c r="F304" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1097</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="11" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C305" s="11" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D305" s="12" t="s">
         <v>5</v>
@@ -11451,82 +11404,82 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B306" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D306" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E306" s="12">
-        <v>15213</v>
+        <v>16701</v>
       </c>
       <c r="F306" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1073</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" s="11" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B307" s="11" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C307" s="11" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D307" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E307" s="12">
-        <v>15243</v>
+        <v>15213</v>
       </c>
       <c r="F307" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1084</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" s="11" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B308" s="11" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D308" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E308" s="12">
-        <v>15260</v>
+        <v>15243</v>
       </c>
       <c r="F308" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" s="11" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B309" s="11" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C309" s="11" t="s">
-        <v>621</v>
+        <v>844</v>
       </c>
       <c r="D309" s="12" t="s">
         <v>5</v>
@@ -11543,19 +11496,19 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="11" t="s">
-        <v>1019</v>
+        <v>845</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>1045</v>
+        <v>846</v>
       </c>
       <c r="C310" s="11" t="s">
-        <v>1020</v>
+        <v>621</v>
       </c>
       <c r="D310" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E310" s="12">
-        <v>15213</v>
+        <v>15260</v>
       </c>
       <c r="F310" s="12" t="s">
         <v>6</v>
@@ -11566,19 +11519,19 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="11" t="s">
-        <v>656</v>
+        <v>1019</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>1066</v>
+        <v>1045</v>
       </c>
       <c r="C311" s="11" t="s">
-        <v>657</v>
+        <v>1020</v>
       </c>
       <c r="D311" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E311" s="12">
-        <v>15261</v>
+        <v>15213</v>
       </c>
       <c r="F311" s="12" t="s">
         <v>6</v>
@@ -11589,13 +11542,13 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" s="11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C312" s="11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D312" s="12" t="s">
         <v>5</v>
@@ -11612,174 +11565,174 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="11" t="s">
-        <v>847</v>
+        <v>658</v>
       </c>
       <c r="B313" s="11" t="s">
-        <v>848</v>
+        <v>1067</v>
       </c>
       <c r="C313" s="11" t="s">
-        <v>849</v>
+        <v>659</v>
       </c>
       <c r="D313" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E313" s="12">
-        <v>15206</v>
+        <v>15261</v>
       </c>
       <c r="F313" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="11" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B314" s="14" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C314" s="14" t="s">
-        <v>1023</v>
+        <v>847</v>
+      </c>
+      <c r="B314" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="C314" s="11" t="s">
+        <v>849</v>
       </c>
       <c r="D314" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E314" s="12">
-        <v>15219</v>
+        <v>15206</v>
       </c>
       <c r="F314" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="B315" s="11" t="s">
-        <v>851</v>
-      </c>
-      <c r="C315" s="11" t="s">
-        <v>852</v>
+        <v>1021</v>
+      </c>
+      <c r="B315" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C315" s="14" t="s">
+        <v>1023</v>
       </c>
       <c r="D315" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E315" s="12">
-        <v>15213</v>
+        <v>15219</v>
       </c>
       <c r="F315" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" s="11" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B316" s="11" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C316" s="11" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D316" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E316" s="12">
-        <v>15208</v>
+        <v>15213</v>
       </c>
       <c r="F316" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" s="11" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D317" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E317" s="12">
-        <v>15213</v>
+        <v>15208</v>
       </c>
       <c r="F317" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" s="11" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D318" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E318" s="12">
-        <v>15904</v>
+        <v>15213</v>
       </c>
       <c r="F318" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" s="11" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B319" s="11" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C319" s="11" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D319" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E319" s="12">
-        <v>16354</v>
+        <v>15904</v>
       </c>
       <c r="F319" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" s="11" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B320" s="11" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C320" s="11" t="s">
-        <v>439</v>
+        <v>863</v>
       </c>
       <c r="D320" s="12" t="s">
         <v>5</v>
@@ -11796,10 +11749,10 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" s="11" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B321" s="11" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>439</v>
@@ -11819,13 +11772,13 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" s="11" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B322" s="11" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>869</v>
+        <v>439</v>
       </c>
       <c r="D322" s="12" t="s">
         <v>5</v>
@@ -11842,13 +11795,13 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" s="11" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="D323" s="12" t="s">
         <v>5</v>
@@ -11865,13 +11818,13 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="11" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>871</v>
       </c>
       <c r="C324" s="11" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D324" s="12" t="s">
         <v>5</v>
@@ -11888,13 +11841,13 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="11" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="D325" s="12" t="s">
         <v>5</v>
@@ -11911,42 +11864,42 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="11" t="s">
-        <v>1130</v>
+        <v>875</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>1025</v>
+        <v>876</v>
       </c>
       <c r="C326" s="11" t="s">
-        <v>61</v>
+        <v>877</v>
       </c>
       <c r="D326" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E326" s="12">
-        <v>15213</v>
+        <v>16354</v>
       </c>
       <c r="F326" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1073</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="11" t="s">
-        <v>878</v>
+        <v>1130</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>879</v>
+        <v>1025</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>880</v>
+        <v>61</v>
       </c>
       <c r="D327" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E327" s="12">
-        <v>15260</v>
+        <v>15213</v>
       </c>
       <c r="F327" s="12" t="s">
         <v>6</v>
@@ -11957,19 +11910,19 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="11" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C328" s="11" t="s">
-        <v>294</v>
+        <v>880</v>
       </c>
       <c r="D328" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E328" s="12">
-        <v>15261</v>
+        <v>15260</v>
       </c>
       <c r="F328" s="12" t="s">
         <v>6</v>
@@ -11980,19 +11933,19 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C329" s="11" t="s">
-        <v>887</v>
+        <v>294</v>
       </c>
       <c r="D329" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E329" s="12">
-        <v>15213</v>
+        <v>15261</v>
       </c>
       <c r="F329" s="12" t="s">
         <v>6</v>
@@ -12003,13 +11956,13 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="11" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D330" s="12" t="s">
         <v>5</v>
@@ -12026,13 +11979,13 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" s="11" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D331" s="12" t="s">
         <v>5</v>
@@ -12049,65 +12002,65 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" s="11" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>1059</v>
+        <v>892</v>
       </c>
       <c r="C332" s="11" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="D332" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E332" s="12">
-        <v>19104</v>
+        <v>15213</v>
       </c>
       <c r="F332" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1095</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" s="11" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>895</v>
+        <v>1059</v>
       </c>
       <c r="C333" s="11" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="D333" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E333" s="12">
-        <v>15213</v>
+        <v>19104</v>
       </c>
       <c r="F333" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1073</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="11" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>838</v>
+        <v>896</v>
       </c>
       <c r="D334" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E334" s="12">
-        <v>15260</v>
+        <v>15213</v>
       </c>
       <c r="F334" s="12" t="s">
         <v>6</v>
@@ -12118,19 +12071,19 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" s="11" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>901</v>
+        <v>838</v>
       </c>
       <c r="D335" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E335" s="12">
-        <v>15213</v>
+        <v>15260</v>
       </c>
       <c r="F335" s="12" t="s">
         <v>6</v>
@@ -12141,197 +12094,197 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" s="11" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D336" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E336" s="12">
-        <v>15238</v>
+        <v>15213</v>
       </c>
       <c r="F336" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G336" s="11" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" s="11" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D337" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E337" s="12">
-        <v>15104</v>
+        <v>15238</v>
       </c>
       <c r="F337" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G337" s="11" t="s">
-        <v>1106</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" s="11" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D338" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E338" s="12">
-        <v>15232</v>
+        <v>15104</v>
       </c>
       <c r="F338" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G338" s="11" t="s">
-        <v>1078</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C339" s="11" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D339" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E339" s="12">
-        <v>15260</v>
+        <v>15232</v>
       </c>
       <c r="F339" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G339" s="11" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" s="11" t="s">
-        <v>182</v>
+        <v>911</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>1047</v>
+        <v>912</v>
       </c>
       <c r="C340" s="11" t="s">
-        <v>183</v>
+        <v>913</v>
       </c>
       <c r="D340" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E340" s="12">
-        <v>15224</v>
+        <v>15260</v>
       </c>
       <c r="F340" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G340" s="11" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C341" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D341" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E341" s="12">
-        <v>15213</v>
+        <v>15224</v>
       </c>
       <c r="F341" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G341" s="11" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" s="11" t="s">
-        <v>914</v>
+        <v>184</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>915</v>
+        <v>1048</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>916</v>
+        <v>185</v>
       </c>
       <c r="D342" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E342" s="12">
-        <v>15235</v>
+        <v>15213</v>
       </c>
       <c r="F342" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G342" s="11" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" s="11" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D343" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E343" s="12">
-        <v>15213</v>
+        <v>15235</v>
       </c>
       <c r="F343" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G343" s="11" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" s="11" t="s">
-        <v>511</v>
+        <v>917</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>1043</v>
+        <v>918</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>512</v>
+        <v>919</v>
       </c>
       <c r="D344" s="12" t="s">
         <v>5</v>
@@ -12348,13 +12301,13 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D345" s="12" t="s">
         <v>5</v>
@@ -12371,36 +12324,36 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" s="11" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="D346" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E346" s="12">
-        <v>15219</v>
+        <v>15213</v>
       </c>
       <c r="F346" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G346" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" s="11" t="s">
-        <v>926</v>
+        <v>546</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>927</v>
+        <v>1042</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>928</v>
+        <v>547</v>
       </c>
       <c r="D347" s="12" t="s">
         <v>5</v>
@@ -12417,36 +12370,36 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" s="11" t="s">
-        <v>568</v>
+        <v>926</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>1041</v>
+        <v>927</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>139</v>
+        <v>928</v>
       </c>
       <c r="D348" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E348" s="12">
-        <v>15213</v>
+        <v>15219</v>
       </c>
       <c r="F348" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G348" s="11" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" s="11" t="s">
-        <v>932</v>
+        <v>568</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>933</v>
+        <v>1041</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>934</v>
+        <v>139</v>
       </c>
       <c r="D349" s="12" t="s">
         <v>5</v>
@@ -12463,36 +12416,36 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" s="11" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D350" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E350" s="12">
-        <v>15232</v>
+        <v>15213</v>
       </c>
       <c r="F350" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G350" s="11" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" s="11" t="s">
-        <v>783</v>
+        <v>935</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>1046</v>
+        <v>936</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>784</v>
+        <v>937</v>
       </c>
       <c r="D351" s="12" t="s">
         <v>5</v>
@@ -12509,174 +12462,174 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" s="11" t="s">
-        <v>950</v>
+        <v>783</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>951</v>
+        <v>1046</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>31</v>
+        <v>784</v>
       </c>
       <c r="D352" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E352" s="12">
-        <v>15260</v>
+        <v>15232</v>
       </c>
       <c r="F352" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G352" s="11" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" s="11" t="s">
-        <v>652</v>
+        <v>950</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>1062</v>
+        <v>951</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>239</v>
+        <v>31</v>
       </c>
       <c r="D353" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E353" s="12">
-        <v>15240</v>
+        <v>15260</v>
       </c>
       <c r="F353" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G353" s="11" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" s="11" t="s">
-        <v>955</v>
+        <v>652</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>956</v>
+        <v>1062</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>957</v>
+        <v>239</v>
       </c>
       <c r="D354" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E354" s="12">
-        <v>15261</v>
+        <v>15240</v>
       </c>
       <c r="F354" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G354" s="11" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" s="11" t="s">
-        <v>920</v>
+        <v>955</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>921</v>
+        <v>956</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>922</v>
+        <v>957</v>
       </c>
       <c r="D355" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E355" s="12">
-        <v>15132</v>
+        <v>15261</v>
       </c>
       <c r="F355" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G355" s="11" t="s">
-        <v>1107</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" s="11" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="D356" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E356" s="12">
-        <v>15219</v>
+        <v>15132</v>
       </c>
       <c r="F356" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G356" s="11" t="s">
-        <v>1075</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" s="11" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="D357" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E357" s="12">
-        <v>15237</v>
+        <v>15219</v>
       </c>
       <c r="F357" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G357" s="11" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" s="11" t="s">
-        <v>708</v>
+        <v>929</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>1051</v>
+        <v>930</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>709</v>
+        <v>931</v>
       </c>
       <c r="D358" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E358" s="12">
-        <v>15213</v>
+        <v>15237</v>
       </c>
       <c r="F358" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G358" s="11" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="11" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D359" s="12" t="s">
         <v>5</v>
@@ -12693,36 +12646,36 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="11" t="s">
-        <v>938</v>
+        <v>706</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>939</v>
+        <v>1034</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>940</v>
+        <v>707</v>
       </c>
       <c r="D360" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E360" s="12">
-        <v>15203</v>
+        <v>15213</v>
       </c>
       <c r="F360" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G360" s="11" t="s">
-        <v>1099</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="11" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B361" s="11" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D361" s="12" t="s">
         <v>5</v>
@@ -12739,502 +12692,502 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="11" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C362" s="11" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D362" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E362" s="12">
-        <v>15213</v>
+        <v>15203</v>
       </c>
       <c r="F362" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G362" s="11" t="s">
-        <v>1073</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="11" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C363" s="11" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D363" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E363" s="12">
-        <v>15219</v>
+        <v>15213</v>
       </c>
       <c r="F363" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G363" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" s="11" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C364" s="11" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D364" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E364" s="12">
-        <v>15206</v>
+        <v>15219</v>
       </c>
       <c r="F364" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G364" s="11" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" s="11" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C365" s="11" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="D365" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E365" s="12">
-        <v>15904</v>
+        <v>15206</v>
       </c>
       <c r="F365" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G365" s="11" t="s">
-        <v>1091</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" s="11" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C366" s="11" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D366" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E366" s="12">
-        <v>16701</v>
+        <v>15904</v>
       </c>
       <c r="F366" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G366" s="11" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" s="11" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>1061</v>
+        <v>961</v>
       </c>
       <c r="C367" s="11" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D367" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E367" s="12">
-        <v>16365</v>
+        <v>16701</v>
       </c>
       <c r="F367" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G367" s="11" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" s="11" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>965</v>
+        <v>1061</v>
       </c>
       <c r="C368" s="11" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D368" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E368" s="12">
-        <v>15301</v>
+        <v>16365</v>
       </c>
       <c r="F368" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G368" s="11" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" s="11" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C369" s="11" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D369" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E369" s="12">
-        <v>15213</v>
+        <v>15301</v>
       </c>
       <c r="F369" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G369" s="11" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" s="11" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C370" s="11" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D370" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E370" s="12">
-        <v>15904</v>
+        <v>15213</v>
       </c>
       <c r="F370" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G370" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" s="11" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C371" s="11" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D371" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E371" s="12">
-        <v>15233</v>
+        <v>15904</v>
       </c>
       <c r="F371" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G371" s="11" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" s="11" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>1060</v>
+        <v>974</v>
       </c>
       <c r="C372" s="11" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D372" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E372" s="12">
-        <v>15260</v>
+        <v>15233</v>
       </c>
       <c r="F372" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G372" s="11" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" s="11" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>979</v>
+        <v>1060</v>
       </c>
       <c r="C373" s="11" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="D373" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E373" s="12">
-        <v>15224</v>
+        <v>15260</v>
       </c>
       <c r="F373" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G373" s="11" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" s="11" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C374" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D374" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E374" s="12">
-        <v>16701</v>
+        <v>15224</v>
       </c>
       <c r="F374" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G374" s="11" t="s">
-        <v>1097</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" s="11" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="C375" s="11" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="D375" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E375" s="12">
-        <v>15233</v>
+        <v>16701</v>
       </c>
       <c r="F375" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G375" s="11" t="s">
-        <v>1079</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" s="11" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C376" s="11" t="s">
-        <v>47</v>
+        <v>986</v>
       </c>
       <c r="D376" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E376" s="12">
-        <v>15601</v>
+        <v>15233</v>
       </c>
       <c r="F376" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G376" s="11" t="s">
-        <v>1092</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" s="11" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C377" s="11" t="s">
-        <v>991</v>
+        <v>47</v>
       </c>
       <c r="D377" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E377" s="12">
-        <v>16701</v>
+        <v>15601</v>
       </c>
       <c r="F377" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G377" s="11" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" s="11" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B378" s="11" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C378" s="11" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D378" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E378" s="12">
-        <v>15904</v>
+        <v>16701</v>
       </c>
       <c r="F378" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G378" s="11" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" s="11" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C379" s="11" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D379" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E379" s="12">
-        <v>16701</v>
+        <v>15904</v>
       </c>
       <c r="F379" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G379" s="11" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" s="11" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B380" s="11" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="C380" s="11" t="s">
-        <v>38</v>
+        <v>995</v>
       </c>
       <c r="D380" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E380" s="12">
-        <v>15260</v>
+        <v>16701</v>
       </c>
       <c r="F380" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G380" s="11" t="s">
-        <v>1073</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" s="11" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B381" s="11" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C381" s="11" t="s">
-        <v>1002</v>
+        <v>38</v>
       </c>
       <c r="D381" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E381" s="12">
-        <v>15904</v>
+        <v>15260</v>
       </c>
       <c r="F381" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G381" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" s="11" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B382" s="11" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C382" s="11" t="s">
-        <v>38</v>
+        <v>1002</v>
       </c>
       <c r="D382" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E382" s="12">
-        <v>15260</v>
+        <v>15904</v>
       </c>
       <c r="F382" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G382" s="11" t="s">
-        <v>1073</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" s="11" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B383" s="11" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>1005</v>
+        <v>38</v>
       </c>
       <c r="D383" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E383" s="12">
-        <v>15213</v>
+        <v>15260</v>
       </c>
       <c r="F383" s="12" t="s">
         <v>6</v>
@@ -13245,13 +13198,13 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" s="11" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B384" s="11" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C384" s="11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="D384" s="12" t="s">
         <v>5</v>
@@ -13268,53 +13221,76 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" s="11" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B385" s="11" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C385" s="11" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D385" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E385" s="12">
-        <v>15904</v>
+        <v>15213</v>
       </c>
       <c r="F385" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G385" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" s="11" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B386" s="11" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C386" s="11" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D386" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E386" s="12">
+        <v>15904</v>
+      </c>
+      <c r="F386" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G386" s="11" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A387" s="11" t="s">
         <v>1011</v>
       </c>
-      <c r="B386" s="11" t="s">
+      <c r="B387" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="C386" s="11" t="s">
+      <c r="C387" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E386" s="12">
+      <c r="D387" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E387" s="12">
         <v>16701</v>
       </c>
-      <c r="F386" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G386" s="11" t="s">
+      <c r="F387" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G387" s="11" t="s">
         <v>1097</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G386">
-    <sortCondition sortBy="cellColor" ref="B2:B386" dxfId="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G387">
+    <sortCondition sortBy="cellColor" ref="B2:B387" dxfId="1"/>
   </sortState>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
